--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487781_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487781_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4638</v>
+        <v>3.9173</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0019</v>
+        <v>3.0719</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4619</v>
+        <v>0.8454</v>
       </c>
       <c r="G2" t="n">
         <v>-1.4859</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>1.9716</v>
+        <v>1.425</v>
       </c>
       <c r="T2" t="n">
-        <v>1.034</v>
+        <v>1.104</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9376</v>
+        <v>0.3211</v>
       </c>
       <c r="V2" t="n">
         <v>2.1051</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4395</v>
+        <v>3.6269</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0974</v>
+        <v>4.1674</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.658</v>
+        <v>-0.5405</v>
       </c>
       <c r="G3" t="n">
         <v>1.4668</v>
@@ -688,13 +688,13 @@
         <v>1.2487</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1402</v>
+        <v>0.3277</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3444</v>
+        <v>0.4144</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2042</v>
+        <v>-0.0867</v>
       </c>
       <c r="V3" t="n">
         <v>0.5838</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7945</v>
+        <v>1.5071</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1905</v>
+        <v>1.8738</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3961</v>
+        <v>-0.3667</v>
       </c>
       <c r="G4" t="n">
         <v>1.0946</v>
@@ -766,13 +766,13 @@
         <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8892</v>
+        <v>0.6018</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1116</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2224</v>
+        <v>-0.193</v>
       </c>
       <c r="V4" t="n">
         <v>-0.8137</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2677</v>
+        <v>0.9508</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8502999999999999</v>
+        <v>1.4746</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5826</v>
+        <v>-0.5238</v>
       </c>
       <c r="G5" t="n">
         <v>0.5178</v>
@@ -844,13 +844,13 @@
         <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.169</v>
+        <v>0.5141</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.5558</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1004</v>
+        <v>-0.0417</v>
       </c>
       <c r="V5" t="n">
         <v>1.1675</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0559</v>
+        <v>0.4338</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9455</v>
+        <v>2.1179</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8896</v>
+        <v>-1.6841</v>
       </c>
       <c r="G6" t="n">
         <v>0.5678</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1768</v>
+        <v>0.2011</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4005</v>
+        <v>0.5729</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5774</v>
+        <v>-0.3718</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1675</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4004</v>
+        <v>0.1955</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6307</v>
+        <v>3.2223</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0311</v>
+        <v>-3.0267</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.7391</v>
+        <v>0.2626</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.034</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.8052</v>
+        <v>0.2286</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4285</v>
+        <v>3.9776</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1683</v>
+        <v>1.1528</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5968</v>
+        <v>2.8248</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.3106</v>
+        <v>-3.7151</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1022</v>
+        <v>-1.1189</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.2084</v>
+        <v>-2.5962</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4162</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3824</v>
+        <v>-0.2345</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8293</v>
+        <v>0.742</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4469</v>
+        <v>-0.9766</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4599</v>
+        <v>0.5838</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>0.5838</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>T. PIERRE PHILIPPE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9897</v>
+        <v>-2.1164</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3306</v>
+        <v>-0.2926</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.3203</v>
+        <v>-1.8238</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2626</v>
+        <v>-2.188</v>
       </c>
       <c r="H8" t="n">
-        <v>0.034</v>
+        <v>-2.4672</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2286</v>
+        <v>0.2792</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9776</v>
+        <v>0.8901</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1528</v>
+        <v>-2.022</v>
       </c>
       <c r="L8" t="n">
-        <v>2.8248</v>
+        <v>2.9122</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.7151</v>
+        <v>-3.0782</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1189</v>
+        <v>-0.4452</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.5962</v>
+        <v>-2.6329</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4162</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.4198</v>
+        <v>0.3828</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.1496</v>
+        <v>0.7716</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.2702</v>
+        <v>-0.3888</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5838</v>
+        <v>0.9376</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5838</v>
+        <v>1.1675</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0992</v>
+        <v>-2.4948</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3791</v>
+        <v>0.6244</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4783</v>
+        <v>-3.1192</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0036</v>
+        <v>-2.7391</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3666</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6369</v>
+        <v>-2.8052</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6214</v>
+        <v>-0.4285</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1623</v>
+        <v>0.1683</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7838000000000001</v>
+        <v>-0.5968</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.625</v>
+        <v>-2.3106</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2043</v>
+        <v>-0.1022</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.4207</v>
+        <v>-2.2084</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4475</v>
+        <v>0.288</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.823</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.535</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>-0.4599</v>
       </c>
       <c r="W9" t="n">
         <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3975</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. FRANCO GARCIA</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8803</v>
+        <v>-2.5926</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2366</v>
+        <v>0.9738</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3563</v>
+        <v>-3.5664</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.8412</v>
+        <v>-2.0036</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0596</v>
+        <v>-0.3666</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.7816</v>
+        <v>-1.6369</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.7799</v>
+        <v>0.6214</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0384</v>
+        <v>-0.1623</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.8183</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0613</v>
+        <v>-2.625</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.098</v>
+        <v>-0.2043</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0367</v>
+        <v>-2.4207</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4554</v>
+        <v>-0.0458</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4567</v>
+        <v>0.1224</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0013</v>
+        <v>-0.1683</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. PIERRE PHILIPPE</t>
+          <t>S. FRANCO GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.209</v>
+        <v>-2.7014</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2384</v>
+        <v>-2.999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9706</v>
+        <v>0.2976</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.188</v>
+        <v>-2.8412</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.4672</v>
+        <v>-0.0596</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2792</v>
+        <v>-2.7816</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8901</v>
+        <v>-2.7799</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.022</v>
+        <v>0.0384</v>
       </c>
       <c r="L11" t="n">
-        <v>2.9122</v>
+        <v>-2.8183</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.0782</v>
+        <v>-0.0613</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4452</v>
+        <v>-0.098</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.6329</v>
+        <v>0.0367</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.2487</v>
+        <v>0.4162</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.8731</v>
+        <v>0.4162</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7098</v>
+        <v>-0.2765</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1743</v>
+        <v>-0.2191</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5356</v>
+        <v>-0.0574</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9376</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1675</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.557200000000002</v>
+        <v>0.7262</v>
       </c>
       <c r="E12" t="n">
-        <v>11.951</v>
+        <v>14.2345</v>
       </c>
       <c r="F12" t="n">
-        <v>-13.5084</v>
+        <v>-13.5082</v>
       </c>
       <c r="G12" t="n">
         <v>-7.3482</v>
@@ -1390,16 +1390,16 @@
         <v>11.4465</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9000999999999997</v>
+        <v>3.1837</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3984</v>
+        <v>5.6819</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.4984</v>
+        <v>-2.4982</v>
       </c>
       <c r="V12" t="n">
-        <v>1.7692</v>
+        <v>1.769200000000001</v>
       </c>
       <c r="W12" t="n">
         <v>6.527700000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.7026</v>
+        <v>5.3373</v>
       </c>
       <c r="E13" t="n">
-        <v>5.893</v>
+        <v>3.5356</v>
       </c>
       <c r="F13" t="n">
-        <v>1.8096</v>
+        <v>1.8018</v>
       </c>
       <c r="G13" t="n">
         <v>3.5427</v>
@@ -1468,13 +1468,13 @@
         <v>1.6649</v>
       </c>
       <c r="S13" t="n">
-        <v>3.9914</v>
+        <v>1.6261</v>
       </c>
       <c r="T13" t="n">
-        <v>3.9567</v>
+        <v>1.5993</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0347</v>
+        <v>0.0268</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2477</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.542</v>
+        <v>2.1619</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1873</v>
+        <v>3.7231</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6453</v>
+        <v>-1.5612</v>
       </c>
       <c r="G14" t="n">
         <v>2.6837</v>
@@ -1546,13 +1546,13 @@
         <v>0.8325</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7254</v>
+        <v>-0.1055</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1338</v>
+        <v>0.402</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5917</v>
+        <v>-0.5075</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1681</v>
+        <v>2.1467</v>
       </c>
       <c r="E15" t="n">
-        <v>2.283</v>
+        <v>2.7117</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1149</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>3.0572</v>
@@ -1624,13 +1624,13 @@
         <v>1.2487</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9297</v>
+        <v>0.0489</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1338</v>
+        <v>0.2948</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7959000000000001</v>
+        <v>-0.2459</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1675</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9089</v>
+        <v>2.1439</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6518</v>
+        <v>3.5091</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7429</v>
+        <v>-1.3652</v>
       </c>
       <c r="G16" t="n">
         <v>0.5197000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6108</v>
+        <v>-0.3758</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9134</v>
+        <v>-0.0562</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6974</v>
+        <v>-0.3196</v>
       </c>
       <c r="V16" t="n">
         <v>1.1675</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4721</v>
+        <v>-0.4633</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.07290000000000001</v>
+        <v>0.1414</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3991</v>
+        <v>-0.6046</v>
       </c>
       <c r="G17" t="n">
         <v>0.531</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1644</v>
+        <v>0.1732</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1305</v>
+        <v>0.0838</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2949</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1675</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. OBAJO BELTRAN</t>
+          <t>A. INFANTE GUTIERREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7942</v>
+        <v>-1.0716</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7389</v>
+        <v>1.0564</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5332</v>
+        <v>-2.1281</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3849</v>
+        <v>0.2692</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7337</v>
+        <v>-0.2108</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.1186</v>
+        <v>0.48</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4602</v>
+        <v>2.1717</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9786</v>
+        <v>0.0915</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5184</v>
+        <v>2.0802</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8451</v>
+        <v>-1.9025</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7551</v>
+        <v>-0.3023</v>
       </c>
       <c r="O18" t="n">
         <v>-1.6002</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.8325</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.2487</v>
+        <v>-1.0406</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4162</v>
+        <v>0.8325</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2844</v>
+        <v>-0.549</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1924</v>
+        <v>-0.0747</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4769</v>
+        <v>-0.4743</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7076</v>
+        <v>-0.5838</v>
       </c>
       <c r="W18" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.6275</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>L. OBAJO BELTRAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5522</v>
+        <v>-1.1744</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0937</v>
+        <v>1.4175</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4584</v>
+        <v>-2.5919</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4515</v>
+        <v>-0.3849</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7478</v>
+        <v>1.7337</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1993</v>
+        <v>-2.1186</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2918</v>
+        <v>0.4602</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4296</v>
+        <v>0.9786</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8621</v>
+        <v>-0.5184</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7433</v>
+        <v>-0.8451</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3182</v>
+        <v>0.7551</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.0614</v>
+        <v>-1.6002</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8731</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4568</v>
+        <v>0.4162</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>-0.6646</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8383</v>
+        <v>-0.129</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4118</v>
+        <v>-0.5356</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.4776</v>
+        <v>0.7076</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1061</v>
+        <v>2.3351</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5838</v>
+        <v>-1.6275</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. INFANTE GUTIERREZ</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1804</v>
+        <v>-2.0474</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4135</v>
+        <v>-1.5223</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5939</v>
+        <v>-0.525</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2692</v>
+        <v>-0.4515</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2108</v>
+        <v>0.7478</v>
       </c>
       <c r="I20" t="n">
-        <v>0.48</v>
+        <v>-1.1993</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1717</v>
+        <v>1.2918</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0915</v>
+        <v>0.4296</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0802</v>
+        <v>0.8621</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9025</v>
+        <v>-1.7433</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3023</v>
+        <v>0.3182</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.6002</v>
+        <v>-2.0614</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2081</v>
+        <v>-1.8731</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-3.3299</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8325</v>
+        <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.6578</v>
+        <v>0.7548</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7177</v>
+        <v>0.4096</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9401</v>
+        <v>0.3452</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5838</v>
+        <v>-0.4776</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.1061</v>
       </c>
       <c r="X20" t="n">
         <v>-0.5838</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7656</v>
+        <v>-4.0473</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4926</v>
+        <v>-1.064</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2729</v>
+        <v>-2.9832</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4189</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.098</v>
+        <v>-0.3797</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.46</v>
+        <v>-0.0314</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.638</v>
+        <v>-0.3483</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.5571</v>
+        <v>2.985799999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>13.5083</v>
+        <v>13.5085</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.951</v>
+        <v>-10.5224</v>
       </c>
       <c r="G22" t="n">
         <v>7.348199999999999</v>
@@ -2170,13 +2170,13 @@
         <v>8.3247</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9002999999999998</v>
+        <v>0.5284000000000002</v>
       </c>
       <c r="T22" t="n">
-        <v>2.498200000000001</v>
+        <v>2.4982</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.3986</v>
+        <v>-1.9698</v>
       </c>
       <c r="V22" t="n">
         <v>-1.769</v>
